--- a/Bases_de_Dados/FootyStats/Romania Liga I_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Romania Liga I_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP228"/>
+  <dimension ref="A1:BP229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.07</v>
@@ -3748,7 +3748,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.13</v>
@@ -10939,7 +10939,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.79</v>
@@ -12032,7 +12032,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR53" t="n">
         <v>1.43</v>
@@ -14427,7 +14427,7 @@
         <v>1.25</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.93</v>
@@ -15084,7 +15084,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR67" t="n">
         <v>1.66</v>
@@ -19005,7 +19005,7 @@
         <v>1.4</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.79</v>
@@ -19662,7 +19662,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR88" t="n">
         <v>1.3</v>
@@ -21624,7 +21624,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR97" t="n">
         <v>1.43</v>
@@ -21839,7 +21839,7 @@
         <v>1.67</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.43</v>
@@ -23368,7 +23368,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR105" t="n">
         <v>1.49</v>
@@ -25330,7 +25330,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR114" t="n">
         <v>1.67</v>
@@ -26635,7 +26635,7 @@
         <v>0.8</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.5</v>
@@ -27289,7 +27289,7 @@
         <v>1.71</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.07</v>
@@ -28164,7 +28164,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR127" t="n">
         <v>1.51</v>
@@ -30780,7 +30780,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR139" t="n">
         <v>1.5</v>
@@ -31649,7 +31649,7 @@
         <v>1.11</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.36</v>
@@ -33396,7 +33396,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR151" t="n">
         <v>1.8</v>
@@ -35355,7 +35355,7 @@
         <v>1.33</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.43</v>
@@ -35794,7 +35794,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR162" t="n">
         <v>1.49</v>
@@ -37971,7 +37971,7 @@
         <v>0.6</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.71</v>
@@ -40372,7 +40372,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR183" t="n">
         <v>1.84</v>
@@ -42113,7 +42113,7 @@
         <v>1.73</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.64</v>
@@ -43642,7 +43642,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR198" t="n">
         <v>1.68</v>
@@ -43857,7 +43857,7 @@
         <v>1.67</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.64</v>
@@ -47127,7 +47127,7 @@
         <v>1.92</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ214" t="n">
         <v>1.79</v>
@@ -47566,7 +47566,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR216" t="n">
         <v>1.4</v>
@@ -50258,6 +50258,224 @@
       </c>
       <c r="BP228" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>8205628</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>46081.625</v>
+      </c>
+      <c r="F229" t="n">
+        <v>29</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>SSC Farul</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>CFR Cluj</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>2</v>
+      </c>
+      <c r="K229" t="n">
+        <v>2</v>
+      </c>
+      <c r="L229" t="n">
+        <v>1</v>
+      </c>
+      <c r="M229" t="n">
+        <v>2</v>
+      </c>
+      <c r="N229" t="n">
+        <v>3</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>['16', '27']</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="R229" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S229" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T229" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U229" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V229" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W229" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X229" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA229" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC229" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM229" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN229" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO229" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BP229" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Romania Liga I_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Romania Liga I_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.64</v>
@@ -2876,7 +2876,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.07</v>
@@ -4620,7 +4620,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR19" t="n">
         <v>0.97</v>
@@ -4835,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.71</v>
@@ -5274,7 +5274,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR22" t="n">
         <v>1.2</v>
@@ -6582,7 +6582,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR28" t="n">
         <v>1.47</v>
@@ -6797,10 +6797,10 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR29" t="n">
         <v>1.38</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.07</v>
@@ -8105,7 +8105,7 @@
         <v>2</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.86</v>
@@ -8980,7 +8980,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR39" t="n">
         <v>1.04</v>
@@ -9198,7 +9198,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR40" t="n">
         <v>1.24</v>
@@ -9413,7 +9413,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.13</v>
@@ -9631,7 +9631,7 @@
         <v>2</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.43</v>
@@ -10506,7 +10506,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR46" t="n">
         <v>1.88</v>
@@ -11157,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.79</v>
@@ -11378,7 +11378,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR50" t="n">
         <v>1.61</v>
@@ -11596,7 +11596,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR51" t="n">
         <v>1.23</v>
@@ -12468,7 +12468,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR55" t="n">
         <v>2.34</v>
@@ -13119,7 +13119,7 @@
         <v>1.75</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.79</v>
@@ -13337,7 +13337,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.71</v>
@@ -13994,7 +13994,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR62" t="n">
         <v>2.11</v>
@@ -14648,7 +14648,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR65" t="n">
         <v>1.39</v>
@@ -14863,10 +14863,10 @@
         <v>1.5</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR66" t="n">
         <v>1.69</v>
@@ -15738,7 +15738,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR70" t="n">
         <v>1.45</v>
@@ -16392,7 +16392,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR73" t="n">
         <v>1.36</v>
@@ -17043,7 +17043,7 @@
         <v>1</v>
       </c>
       <c r="AP76" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.93</v>
@@ -17915,7 +17915,7 @@
         <v>0.8</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.86</v>
@@ -18136,7 +18136,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR81" t="n">
         <v>1.72</v>
@@ -18569,10 +18569,10 @@
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR83" t="n">
         <v>1.76</v>
@@ -18790,7 +18790,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR84" t="n">
         <v>1.59</v>
@@ -19877,7 +19877,7 @@
         <v>1.83</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.64</v>
@@ -21842,7 +21842,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR98" t="n">
         <v>2.05</v>
@@ -22496,7 +22496,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR101" t="n">
         <v>1.4</v>
@@ -22711,7 +22711,7 @@
         <v>0.4</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.07</v>
@@ -22929,10 +22929,10 @@
         <v>2.33</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR103" t="n">
         <v>1.58</v>
@@ -23150,7 +23150,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR104" t="n">
         <v>1.64</v>
@@ -25327,7 +25327,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.53</v>
@@ -25545,10 +25545,10 @@
         <v>1.57</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR115" t="n">
         <v>1.6</v>
@@ -25766,7 +25766,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR116" t="n">
         <v>1.22</v>
@@ -25981,7 +25981,7 @@
         <v>0.33</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.13</v>
@@ -26420,7 +26420,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR119" t="n">
         <v>1.59</v>
@@ -26638,7 +26638,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR120" t="n">
         <v>1.9</v>
@@ -27725,10 +27725,10 @@
         <v>0.67</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR125" t="n">
         <v>1.68</v>
@@ -27946,7 +27946,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR126" t="n">
         <v>1.64</v>
@@ -28161,7 +28161,7 @@
         <v>0.57</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.53</v>
@@ -28600,7 +28600,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR129" t="n">
         <v>1.59</v>
@@ -29251,7 +29251,7 @@
         <v>1.63</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.79</v>
@@ -29908,7 +29908,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR135" t="n">
         <v>2.02</v>
@@ -30562,7 +30562,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR138" t="n">
         <v>1.56</v>
@@ -30995,7 +30995,7 @@
         <v>1.13</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.07</v>
@@ -31431,7 +31431,7 @@
         <v>1.5</v>
       </c>
       <c r="AP142" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.07</v>
@@ -31652,7 +31652,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR143" t="n">
         <v>1.83</v>
@@ -32524,7 +32524,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR147" t="n">
         <v>1.5</v>
@@ -33611,7 +33611,7 @@
         <v>1.11</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.93</v>
@@ -33832,7 +33832,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR153" t="n">
         <v>1.46</v>
@@ -34050,7 +34050,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR154" t="n">
         <v>2.01</v>
@@ -34919,7 +34919,7 @@
         <v>0.22</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.13</v>
@@ -35573,10 +35573,10 @@
         <v>1.3</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR161" t="n">
         <v>1.42</v>
@@ -36230,7 +36230,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR164" t="n">
         <v>1.51</v>
@@ -36445,7 +36445,7 @@
         <v>1.7</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.64</v>
@@ -37102,7 +37102,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR168" t="n">
         <v>1.9</v>
@@ -37320,7 +37320,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR169" t="n">
         <v>1.87</v>
@@ -37538,7 +37538,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR170" t="n">
         <v>1.42</v>
@@ -37753,7 +37753,7 @@
         <v>1.3</v>
       </c>
       <c r="AP171" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.43</v>
@@ -38843,7 +38843,7 @@
         <v>1.9</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.79</v>
@@ -39282,7 +39282,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR178" t="n">
         <v>1.36</v>
@@ -40590,7 +40590,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR184" t="n">
         <v>1.6</v>
@@ -40805,10 +40805,10 @@
         <v>1.73</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR185" t="n">
         <v>1.69</v>
@@ -41241,7 +41241,7 @@
         <v>1</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ187" t="n">
         <v>0.93</v>
@@ -41459,7 +41459,7 @@
         <v>0.64</v>
       </c>
       <c r="AP188" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.71</v>
@@ -42334,7 +42334,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ192" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR192" t="n">
         <v>1.86</v>
@@ -42988,7 +42988,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR195" t="n">
         <v>1.19</v>
@@ -43206,7 +43206,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR196" t="n">
         <v>1.45</v>
@@ -43424,7 +43424,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR197" t="n">
         <v>1.3</v>
@@ -43639,7 +43639,7 @@
         <v>1.17</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.53</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ204" t="n">
         <v>0.86</v>
@@ -45822,7 +45822,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR208" t="n">
         <v>1.65</v>
@@ -46037,7 +46037,7 @@
         <v>1.58</v>
       </c>
       <c r="AP209" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ209" t="n">
         <v>1.64</v>
@@ -46258,7 +46258,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR210" t="n">
         <v>1.49</v>
@@ -46694,7 +46694,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ212" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR212" t="n">
         <v>1.2</v>
@@ -46909,7 +46909,7 @@
         <v>1.23</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ213" t="n">
         <v>1.07</v>
@@ -47130,7 +47130,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ214" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR214" t="n">
         <v>1.64</v>
@@ -47348,7 +47348,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR215" t="n">
         <v>1.8</v>
@@ -47781,7 +47781,7 @@
         <v>0.85</v>
       </c>
       <c r="AP217" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ217" t="n">
         <v>0.79</v>
@@ -49089,7 +49089,7 @@
         <v>1.54</v>
       </c>
       <c r="AP223" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ223" t="n">
         <v>1.64</v>
@@ -50476,6 +50476,878 @@
       </c>
       <c r="BP229" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>8205735</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>46082.44791666666</v>
+      </c>
+      <c r="F230" t="n">
+        <v>29</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Petrolul 52</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Csikszereda</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="n">
+        <v>1</v>
+      </c>
+      <c r="N230" t="n">
+        <v>2</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R230" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S230" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U230" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V230" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X230" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA230" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC230" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE230" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BI230" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BJ230" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BK230" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BL230" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BM230" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BN230" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BO230" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP230" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>8205734</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>46082.54166666666</v>
+      </c>
+      <c r="F231" t="n">
+        <v>29</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Dinamo Bucureşti</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Argeș</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="n">
+        <v>1</v>
+      </c>
+      <c r="N231" t="n">
+        <v>1</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R231" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S231" t="n">
+        <v>5</v>
+      </c>
+      <c r="T231" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U231" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V231" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W231" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X231" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA231" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB231" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC231" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE231" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF231" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG231" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH231" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI231" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ231" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK231" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL231" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM231" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN231" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO231" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP231" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>8205629</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>46082.66666666666</v>
+      </c>
+      <c r="F232" t="n">
+        <v>29</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>UTA Arad</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>1</v>
+      </c>
+      <c r="J232" t="n">
+        <v>3</v>
+      </c>
+      <c r="K232" t="n">
+        <v>4</v>
+      </c>
+      <c r="L232" t="n">
+        <v>2</v>
+      </c>
+      <c r="M232" t="n">
+        <v>4</v>
+      </c>
+      <c r="N232" t="n">
+        <v>6</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>['17', '87']</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>['11', '25', '33', '62']</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R232" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S232" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T232" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U232" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V232" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W232" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X232" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ232" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AT232" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AU232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV232" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY232" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB232" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC232" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD232" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE232" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF232" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BG232" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH232" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI232" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ232" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK232" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL232" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM232" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN232" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO232" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP232" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>8205626</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>46083.60416666666</v>
+      </c>
+      <c r="F233" t="n">
+        <v>29</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Unirea Slobozia</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Rapid Bucureşti</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" t="n">
+        <v>1</v>
+      </c>
+      <c r="L233" t="n">
+        <v>1</v>
+      </c>
+      <c r="M233" t="n">
+        <v>2</v>
+      </c>
+      <c r="N233" t="n">
+        <v>3</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>['24', '67']</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="R233" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S233" t="n">
+        <v>2</v>
+      </c>
+      <c r="T233" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U233" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V233" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W233" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X233" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS233" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT233" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU233" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY233" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA233" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB233" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC233" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE233" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="BF233" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG233" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH233" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI233" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ233" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BK233" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BL233" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM233" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN233" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO233" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BP233" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Romania Liga I_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Romania Liga I_20252026.xlsx
@@ -50636,13 +50636,13 @@
         <v>3</v>
       </c>
       <c r="AW230" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX230" t="n">
         <v>3</v>
       </c>
       <c r="AY230" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ230" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Romania Liga I_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Romania Liga I_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.79</v>
@@ -1786,7 +1786,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.64</v>
@@ -3094,7 +3094,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR18" t="n">
         <v>1.25</v>
@@ -4617,7 +4617,7 @@
         <v>3</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.87</v>
@@ -5056,7 +5056,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR21" t="n">
         <v>2.49</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.79</v>
@@ -6364,7 +6364,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR27" t="n">
         <v>1.18</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.64</v>
@@ -8108,7 +8108,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR35" t="n">
         <v>1.63</v>
@@ -8326,7 +8326,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR36" t="n">
         <v>2.47</v>
@@ -8977,7 +8977,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.53</v>
@@ -9634,7 +9634,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR42" t="n">
         <v>1.48</v>
@@ -10067,7 +10067,7 @@
         <v>2</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.64</v>
@@ -11375,7 +11375,7 @@
         <v>2.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.87</v>
@@ -11593,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.53</v>
@@ -12250,7 +12250,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR54" t="n">
         <v>1.49</v>
@@ -12686,7 +12686,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR56" t="n">
         <v>1.67</v>
@@ -12904,7 +12904,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR57" t="n">
         <v>1.73</v>
@@ -13773,7 +13773,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.64</v>
@@ -14209,7 +14209,7 @@
         <v>0.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.07</v>
@@ -14430,7 +14430,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR64" t="n">
         <v>1.84</v>
@@ -15081,7 +15081,7 @@
         <v>0.5</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.53</v>
@@ -15520,7 +15520,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR69" t="n">
         <v>1.64</v>
@@ -15735,7 +15735,7 @@
         <v>1.25</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.47</v>
@@ -16389,7 +16389,7 @@
         <v>1.2</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.47</v>
@@ -17046,7 +17046,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR76" t="n">
         <v>1.86</v>
@@ -17264,7 +17264,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR77" t="n">
         <v>1.94</v>
@@ -17697,7 +17697,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.13</v>
@@ -17918,7 +17918,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR80" t="n">
         <v>1.69</v>
@@ -19441,7 +19441,7 @@
         <v>1.25</v>
       </c>
       <c r="AP87" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.07</v>
@@ -20095,7 +20095,7 @@
         <v>1.67</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.79</v>
@@ -20316,7 +20316,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR91" t="n">
         <v>1.6</v>
@@ -20534,7 +20534,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR92" t="n">
         <v>1.65</v>
@@ -21403,10 +21403,10 @@
         <v>1.2</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR96" t="n">
         <v>1.45</v>
@@ -21621,7 +21621,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.53</v>
@@ -22493,7 +22493,7 @@
         <v>1</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.47</v>
@@ -23583,10 +23583,10 @@
         <v>1.14</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR106" t="n">
         <v>1.46</v>
@@ -24240,7 +24240,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR109" t="n">
         <v>1.91</v>
@@ -24455,7 +24455,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.64</v>
@@ -24676,7 +24676,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR111" t="n">
         <v>1.95</v>
@@ -24891,7 +24891,7 @@
         <v>0.71</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.71</v>
@@ -28382,7 +28382,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR128" t="n">
         <v>1.73</v>
@@ -28815,7 +28815,7 @@
         <v>1</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.79</v>
@@ -29472,7 +29472,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR133" t="n">
         <v>2.06</v>
@@ -29690,7 +29690,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR134" t="n">
         <v>1.46</v>
@@ -30123,7 +30123,7 @@
         <v>0.63</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.71</v>
@@ -30341,7 +30341,7 @@
         <v>1.88</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.64</v>
@@ -31216,7 +31216,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR141" t="n">
         <v>1.53</v>
@@ -32521,7 +32521,7 @@
         <v>1.56</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.53</v>
@@ -33175,10 +33175,10 @@
         <v>1</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR150" t="n">
         <v>1.26</v>
@@ -33614,7 +33614,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR152" t="n">
         <v>1.66</v>
@@ -33829,7 +33829,7 @@
         <v>2</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.87</v>
@@ -35358,7 +35358,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR160" t="n">
         <v>1.79</v>
@@ -35791,7 +35791,7 @@
         <v>0.8</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.53</v>
@@ -36009,7 +36009,7 @@
         <v>0.8</v>
       </c>
       <c r="AP163" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.79</v>
@@ -36666,7 +36666,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR166" t="n">
         <v>1.45</v>
@@ -36884,7 +36884,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR167" t="n">
         <v>1.17</v>
@@ -37756,7 +37756,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR171" t="n">
         <v>1.32</v>
@@ -38407,7 +38407,7 @@
         <v>1.6</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.07</v>
@@ -39279,7 +39279,7 @@
         <v>1.55</v>
       </c>
       <c r="AP178" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.53</v>
@@ -40154,7 +40154,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR182" t="n">
         <v>1.34</v>
@@ -41244,7 +41244,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR187" t="n">
         <v>1.8</v>
@@ -41680,7 +41680,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR189" t="n">
         <v>1.38</v>
@@ -42549,7 +42549,7 @@
         <v>1.09</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ193" t="n">
         <v>1.07</v>
@@ -43421,7 +43421,7 @@
         <v>0.33</v>
       </c>
       <c r="AP197" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.53</v>
@@ -44732,7 +44732,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ203" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR203" t="n">
         <v>1.65</v>
@@ -44950,7 +44950,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR204" t="n">
         <v>1.28</v>
@@ -45165,10 +45165,10 @@
         <v>1.58</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR205" t="n">
         <v>1.4</v>
@@ -45601,7 +45601,7 @@
         <v>0.17</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.13</v>
@@ -46473,7 +46473,7 @@
         <v>1</v>
       </c>
       <c r="AP211" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.07</v>
@@ -48002,7 +48002,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR218" t="n">
         <v>1.61</v>
@@ -48217,7 +48217,7 @@
         <v>1.69</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ219" t="n">
         <v>1.79</v>
@@ -48438,7 +48438,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ220" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR220" t="n">
         <v>1.9</v>
@@ -48874,7 +48874,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ222" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR222" t="n">
         <v>1.37</v>
@@ -49307,7 +49307,7 @@
         <v>0.77</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ224" t="n">
         <v>0.71</v>
@@ -51348,6 +51348,660 @@
       </c>
       <c r="BP233" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>8205664</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>46087.60416666666</v>
+      </c>
+      <c r="F234" t="n">
+        <v>30</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Csikszereda</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>SSC Farul</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="n">
+        <v>1</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R234" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S234" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T234" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U234" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V234" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W234" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X234" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU234" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW234" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX234" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY234" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ234" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA234" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB234" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC234" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD234" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BE234" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF234" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BG234" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH234" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="BI234" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ234" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK234" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL234" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM234" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN234" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO234" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP234" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="n">
+        <v>8205582</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>46088.39583333334</v>
+      </c>
+      <c r="F235" t="n">
+        <v>30</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Metaloglobus</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>UTA Arad</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>1</v>
+      </c>
+      <c r="J235" t="n">
+        <v>1</v>
+      </c>
+      <c r="K235" t="n">
+        <v>2</v>
+      </c>
+      <c r="L235" t="n">
+        <v>2</v>
+      </c>
+      <c r="M235" t="n">
+        <v>2</v>
+      </c>
+      <c r="N235" t="n">
+        <v>4</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>['9', '72']</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>['44', '61']</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="R235" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S235" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T235" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U235" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V235" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W235" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X235" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY235" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA235" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB235" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC235" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD235" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE235" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF235" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG235" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH235" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BI235" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ235" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK235" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BL235" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM235" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BN235" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO235" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BP235" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="n">
+        <v>8205738</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>46088.5</v>
+      </c>
+      <c r="F236" t="n">
+        <v>30</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Botoşani</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Petrolul 52</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>1</v>
+      </c>
+      <c r="K236" t="n">
+        <v>1</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="n">
+        <v>1</v>
+      </c>
+      <c r="N236" t="n">
+        <v>1</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R236" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S236" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="T236" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U236" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V236" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W236" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X236" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA236" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB236" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC236" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BE236" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF236" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BG236" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BH236" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BI236" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ236" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BK236" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BL236" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BM236" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN236" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO236" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BP236" t="n">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Romania Liga I_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Romania Liga I_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP236"/>
+  <dimension ref="A1:BP237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.71</v>
@@ -5053,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.8</v>
@@ -5928,7 +5928,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR25" t="n">
         <v>0.83</v>
@@ -7018,7 +7018,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR30" t="n">
         <v>1.79</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.79</v>
@@ -10942,7 +10942,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR48" t="n">
         <v>1.49</v>
@@ -12465,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.53</v>
@@ -13122,7 +13122,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR58" t="n">
         <v>2.09</v>
@@ -16610,7 +16610,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR74" t="n">
         <v>1.63</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.07</v>
@@ -20098,7 +20098,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR90" t="n">
         <v>1.47</v>
@@ -20967,7 +20967,7 @@
         <v>1.6</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.64</v>
@@ -24022,7 +24022,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR108" t="n">
         <v>1.5</v>
@@ -24673,7 +24673,7 @@
         <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.4</v>
@@ -29254,7 +29254,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR132" t="n">
         <v>1.68</v>
@@ -29469,7 +29469,7 @@
         <v>1.13</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.07</v>
@@ -32739,7 +32739,7 @@
         <v>1.78</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.64</v>
@@ -34704,7 +34704,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR157" t="n">
         <v>1.41</v>
@@ -37099,7 +37099,7 @@
         <v>1.9</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.87</v>
@@ -38846,7 +38846,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR176" t="n">
         <v>1.71</v>
@@ -40369,7 +40369,7 @@
         <v>1</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.53</v>
@@ -41898,7 +41898,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR190" t="n">
         <v>1.64</v>
@@ -42331,7 +42331,7 @@
         <v>0.36</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ192" t="n">
         <v>0.53</v>
@@ -44293,7 +44293,7 @@
         <v>1.33</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ201" t="n">
         <v>1.07</v>
@@ -45386,7 +45386,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR206" t="n">
         <v>1.96</v>
@@ -48220,7 +48220,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ219" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR219" t="n">
         <v>1.58</v>
@@ -49525,7 +49525,7 @@
         <v>0.15</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ225" t="n">
         <v>0.13</v>
@@ -51738,13 +51738,13 @@
         <v>19</v>
       </c>
       <c r="BA235" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB235" t="n">
         <v>6</v>
       </c>
       <c r="BC235" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD235" t="n">
         <v>3.2</v>
@@ -52002,6 +52002,224 @@
       </c>
       <c r="BP236" t="n">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="n">
+        <v>8205583</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>46088.625</v>
+      </c>
+      <c r="F237" t="n">
+        <v>30</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Universitatea Cluj</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>1</v>
+      </c>
+      <c r="J237" t="n">
+        <v>2</v>
+      </c>
+      <c r="K237" t="n">
+        <v>3</v>
+      </c>
+      <c r="L237" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" t="n">
+        <v>3</v>
+      </c>
+      <c r="N237" t="n">
+        <v>4</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>['24', '40', '57']</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R237" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S237" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="T237" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U237" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V237" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W237" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X237" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AK237" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM237" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AN237" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO237" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AP237" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ237" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR237" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS237" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT237" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AU237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV237" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW237" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX237" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY237" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ237" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA237" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB237" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC237" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD237" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE237" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="BF237" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="BG237" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH237" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI237" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ237" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BK237" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL237" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM237" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN237" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO237" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BP237" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
